--- a/11_Post_Announcement_v2/Project_Southeast_Asia_v2_Financial_Model.xlsx
+++ b/11_Post_Announcement_v2/Project_Southeast_Asia_v2_Financial_Model.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="383">
   <si>
     <t xml:space="preserve">Project Southeast Asia — v2 Financial Model (post-announcement)</t>
   </si>
@@ -55,7 +55,7 @@
     <t xml:space="preserve">COLOUR CODE: blue = hard-coded input; black = formula; green = link to another sheet; yellow fill = key output or input to scrutinise first. CLASSIFICATIONS: PUBLIC FACT, REPORTED (corroborated or single-source), ANALYST CALCULATION, ILLUSTRATIVE ASSUMPTION, UNAVAILABLE.</t>
   </si>
   <si>
-    <t xml:space="preserve">REPORTED FINANCIALS: FY2024-FY2025 revenue and EBITDA are NOT in AkzoNobel's release. They are reported by PCI Magazine and, attributed to Nippon Paint's own statement, by Investing.com, Yahoo Finance UK and Yahoo Finance Singapore. The primary Nippon Paint release was not accessed, so these stay REPORTED, not PUBLIC FACT. The 2026 revenue (&gt;~USD 330m) and ~26% margin are single-source (PCI).</t>
+    <t xml:space="preserve">REPORTED FINANCIALS: FY2024-FY2025 revenue and EBITDA are NOT in AkzoNobel's release. They are reported by several outlets, attributed to Nippon Paint (Investing.com and Yahoo Finance UK attribute them to Nippon Paint; Yahoo Finance Singapore gives them without a named source; PCI Magazine's own attribution could not be re-read on 2026-10-09 because the page returned HTTP 403). The primary Nippon Paint release was not read, so these stay REPORTED, not PUBLIC FACT. The 2026 revenue (&gt;~USD 330m) and ~26% margin are single-source (PCI); not found in five other outlets checked.</t>
   </si>
   <si>
     <t xml:space="preserve">STANDALONE COST RISK: AkzoNobel keeps Global Business Services. TSA and stranded costs are shown inside the case margin (they do not reduce EBITDA a second time); the allowance for standalone-cost risk is the Downside margin step-down.</t>
@@ -169,13 +169,13 @@
     <t xml:space="preserve">Revenue FY2024 (USD m)</t>
   </si>
   <si>
-    <t xml:space="preserve">PCI Magazine (SRC-039) and Yahoo Finance Singapore / MT Newswires (SRC-042), the latter attributing it to the Nippon Paint press release. Primary release not accessed; AkzoNobel's own release states no revenue.</t>
+    <t xml:space="preserve">PCI Magazine (SRC-039) and Yahoo Finance Singapore / MT Newswires (SRC-042; gives the figure without naming a source). Primary Nippon Paint release not read; not in AkzoNobel's release.</t>
   </si>
   <si>
     <t xml:space="preserve">Revenue FY2025 (USD m)</t>
   </si>
   <si>
-    <t xml:space="preserve">PCI Magazine (SRC-039); Investing.com (SRC-041), Yahoo Finance UK (SRC-043) and Yahoo Finance Singapore (SRC-042), each attributing to Nippon Paint.</t>
+    <t xml:space="preserve">PCI Magazine (SRC-039); Investing.com (SRC-041) and Yahoo Finance UK (SRC-043), both attributing it to Nippon Paint without saying whether from a press release; Yahoo Finance Singapore (SRC-042) gives it unattributed. Primary Nippon Paint release not read.</t>
   </si>
   <si>
     <t xml:space="preserve">EBITDA FY2024 (USD m)</t>
@@ -1000,18 +1000,18 @@
     <t xml:space="preserve">Reverse DCF: terminal value (undiscounted) needed to reach the announced EV</t>
   </si>
   <si>
+    <t xml:space="preserve">  Terminal EBITDA margin needed, holding terminal growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Terminal growth needed, holding the case terminal margin</t>
+  </si>
+  <si>
     <t xml:space="preserve">Case 2: Buyer</t>
   </si>
   <si>
     <t xml:space="preserve">Case 3: Downside</t>
   </si>
   <si>
-    <t xml:space="preserve">  Terminal EBITDA margin needed, holding terminal growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Terminal growth needed, holding the case terminal margin</t>
-  </si>
-  <si>
     <t xml:space="preserve">Source ID</t>
   </si>
   <si>
@@ -1126,7 +1126,7 @@
     <t xml:space="preserve">sg.finance.yahoo.com/news/nippon-paint-buy-akzonobel-apos-014603443.html</t>
   </si>
   <si>
-    <t xml:space="preserve">FY2024 and FY2025 revenue/EBITDA, attributed to the Nippon Paint press release</t>
+    <t xml:space="preserve">FY2024 and FY2025 revenue/EBITDA, reported without a named source (not attributed to a press release in the article)</t>
   </si>
   <si>
     <t xml:space="preserve">SRC-043</t>
@@ -1396,7 +1396,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="45">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1575,14 +1575,6 @@
     </xf>
     <xf numFmtId="175" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2107,7 +2099,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>362</v>
       </c>
@@ -6321,7 +6313,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -6361,11 +6353,11 @@
         <v>712.653406213068</v>
       </c>
       <c r="C5" s="31" t="n">
-        <f aca="false">$B$61</f>
+        <f aca="false">$B$66</f>
         <v>853.744956789202</v>
       </c>
       <c r="D5" s="31" t="n">
-        <f aca="false">$B$87</f>
+        <f aca="false">$B$97</f>
         <v>586.198421109987</v>
       </c>
     </row>
@@ -6378,11 +6370,11 @@
         <v>618.105902335867</v>
       </c>
       <c r="C6" s="19" t="n">
-        <f aca="false">$B$63</f>
+        <f aca="false">$B$68</f>
         <v>741.287696792603</v>
       </c>
       <c r="D6" s="19" t="n">
-        <f aca="false">$B$89</f>
+        <f aca="false">$B$99</f>
         <v>509.658320109114</v>
       </c>
     </row>
@@ -6395,11 +6387,11 @@
         <v>845.996667479824</v>
       </c>
       <c r="C7" s="19" t="n">
-        <f aca="false">$B$64</f>
+        <f aca="false">$B$69</f>
         <v>1012.33076501811</v>
       </c>
       <c r="D7" s="19" t="n">
-        <f aca="false">$B$90</f>
+        <f aca="false">$B$100</f>
         <v>694.097258352378</v>
       </c>
     </row>
@@ -6412,11 +6404,11 @@
         <v>0.780823688561554</v>
       </c>
       <c r="C8" s="18" t="n">
-        <f aca="false">$B$62</f>
+        <f aca="false">$B$67</f>
         <v>0.773071133905557</v>
       </c>
       <c r="D8" s="18" t="n">
-        <f aca="false">$B$88</f>
+        <f aca="false">$B$98</f>
         <v>0.769773123369036</v>
       </c>
     </row>
@@ -6429,11 +6421,11 @@
         <v>271.6</v>
       </c>
       <c r="C9" s="19" t="n">
-        <f aca="false">$B$43</f>
+        <f aca="false">$B$48</f>
         <v>293.333333333333</v>
       </c>
       <c r="D9" s="19" t="n">
-        <f aca="false">$B$69</f>
+        <f aca="false">$B$79</f>
         <v>266.426666666667</v>
       </c>
     </row>
@@ -6446,11 +6438,11 @@
         <v>60.6666666666667</v>
       </c>
       <c r="C10" s="19" t="n">
-        <f aca="false">$B$45</f>
+        <f aca="false">$B$50</f>
         <v>76.2666666666667</v>
       </c>
       <c r="D10" s="19" t="n">
-        <f aca="false">$B$71</f>
+        <f aca="false">$B$81</f>
         <v>56.8468444444445</v>
       </c>
     </row>
@@ -6463,11 +6455,11 @@
         <v>0.223367697594502</v>
       </c>
       <c r="C11" s="24" t="n">
-        <f aca="false">$B$57</f>
+        <f aca="false">$B$62</f>
         <v>0.241683848797251</v>
       </c>
       <c r="D11" s="24" t="n">
-        <f aca="false">$B$83</f>
+        <f aca="false">$B$93</f>
         <v>0.203367697594502</v>
       </c>
     </row>
@@ -6928,912 +6920,942 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="B40" s="45" t="n">
+      <c r="B40" s="24" t="n">
         <f aca="false">(((B39*(Assumptions!$B$92-Assumptions!$B$93)/F17+Assumptions!$B$93*Working_Capital!$B$16)/(1+Assumptions!$B$93))-Assumptions!$B$100+Assumptions!$B$106)/(1-Assumptions!$B$66)+Assumptions!$B$100</f>
         <v>0.386708187555486</v>
       </c>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="B41" s="24" t="n">
+        <f aca="false">(B39*Assumptions!$B$92-F17*B32)/(F17*(B32-Working_Capital!$B$16)+B39)</f>
+        <v>0.0571612955661382</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B41" s="46" t="s">
+      <c r="B46" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C46" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D46" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E46" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F46" s="6" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="9" t="s">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="B42" s="29" t="n">
+      <c r="B47" s="29" t="n">
         <f aca="false">Case_Drivers!$B$7</f>
         <v>0.134020618556701</v>
       </c>
-      <c r="C42" s="29" t="n">
+      <c r="C47" s="29" t="n">
         <f aca="false">Case_Drivers!$C$7</f>
         <v>0.05</v>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D47" s="29" t="n">
         <f aca="false">Case_Drivers!$D$7</f>
         <v>0.05</v>
       </c>
-      <c r="E42" s="29" t="n">
+      <c r="E47" s="29" t="n">
         <f aca="false">Case_Drivers!$E$7</f>
         <v>0.05</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F47" s="29" t="n">
         <f aca="false">Case_Drivers!$F$7</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="27" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="27" t="s">
         <v>226</v>
       </c>
-      <c r="B43" s="31" t="n">
-        <f aca="false">Assumptions!$B$26*(1+B42)</f>
+      <c r="B48" s="31" t="n">
+        <f aca="false">Assumptions!$B$26*(1+B47)</f>
         <v>293.333333333333</v>
       </c>
-      <c r="C43" s="31" t="n">
-        <f aca="false">B43*(1+C42)</f>
+      <c r="C48" s="31" t="n">
+        <f aca="false">B48*(1+C47)</f>
         <v>308</v>
       </c>
-      <c r="D43" s="31" t="n">
-        <f aca="false">C43*(1+D42)</f>
+      <c r="D48" s="31" t="n">
+        <f aca="false">C48*(1+D47)</f>
         <v>323.4</v>
       </c>
-      <c r="E43" s="31" t="n">
-        <f aca="false">D43*(1+E42)</f>
+      <c r="E48" s="31" t="n">
+        <f aca="false">D48*(1+E47)</f>
         <v>339.57</v>
       </c>
-      <c r="F43" s="31" t="n">
-        <f aca="false">E43*(1+F42)</f>
+      <c r="F48" s="31" t="n">
+        <f aca="false">E48*(1+F47)</f>
         <v>356.5485</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="B44" s="29" t="n">
+      <c r="B49" s="29" t="n">
         <f aca="false">Case_Drivers!$B$13</f>
         <v>0.26</v>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C49" s="29" t="n">
         <f aca="false">Case_Drivers!$C$13</f>
         <v>0.255420962199313</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D49" s="29" t="n">
         <f aca="false">Case_Drivers!$D$13</f>
         <v>0.250841924398625</v>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E49" s="29" t="n">
         <f aca="false">Case_Drivers!$E$13</f>
         <v>0.246262886597938</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F49" s="29" t="n">
         <f aca="false">Case_Drivers!$F$13</f>
         <v>0.241683848797251</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="27" t="s">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="27" t="s">
         <v>244</v>
       </c>
-      <c r="B45" s="31" t="n">
-        <f aca="false">B43*B44</f>
+      <c r="B50" s="31" t="n">
+        <f aca="false">B48*B49</f>
         <v>76.2666666666667</v>
       </c>
-      <c r="C45" s="31" t="n">
-        <f aca="false">C43*C44</f>
+      <c r="C50" s="31" t="n">
+        <f aca="false">C48*C49</f>
         <v>78.6696563573883</v>
       </c>
-      <c r="D45" s="31" t="n">
-        <f aca="false">D43*D44</f>
+      <c r="D50" s="31" t="n">
+        <f aca="false">D48*D49</f>
         <v>81.1222783505155</v>
       </c>
-      <c r="E45" s="31" t="n">
-        <f aca="false">E43*E44</f>
+      <c r="E50" s="31" t="n">
+        <f aca="false">E48*E49</f>
         <v>83.6234884020619</v>
       </c>
-      <c r="F45" s="31" t="n">
-        <f aca="false">F43*F44</f>
+      <c r="F50" s="31" t="n">
+        <f aca="false">F48*F49</f>
         <v>86.1720137628866</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="B46" s="19" t="n">
-        <f aca="false">B43*Assumptions!$B$100</f>
-        <v>7.33333333333333</v>
-      </c>
-      <c r="C46" s="19" t="n">
-        <f aca="false">C43*Assumptions!$B$100</f>
-        <v>7.7</v>
-      </c>
-      <c r="D46" s="19" t="n">
-        <f aca="false">D43*Assumptions!$B$100</f>
-        <v>8.085</v>
-      </c>
-      <c r="E46" s="19" t="n">
-        <f aca="false">E43*Assumptions!$B$100</f>
-        <v>8.48925</v>
-      </c>
-      <c r="F46" s="19" t="n">
-        <f aca="false">F43*Assumptions!$B$100</f>
-        <v>8.9137125</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="B47" s="19" t="n">
-        <f aca="false">B45-B46</f>
-        <v>68.9333333333333</v>
-      </c>
-      <c r="C47" s="19" t="n">
-        <f aca="false">C45-C46</f>
-        <v>70.9696563573883</v>
-      </c>
-      <c r="D47" s="19" t="n">
-        <f aca="false">D45-D46</f>
-        <v>73.0372783505155</v>
-      </c>
-      <c r="E47" s="19" t="n">
-        <f aca="false">E45-E46</f>
-        <v>75.1342384020619</v>
-      </c>
-      <c r="F47" s="19" t="n">
-        <f aca="false">F45-F46</f>
-        <v>77.2583012628866</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="B48" s="19" t="n">
-        <f aca="false">MAX(B47,0)*Assumptions!$B$66</f>
-        <v>15.1929066666667</v>
-      </c>
-      <c r="C48" s="19" t="n">
-        <f aca="false">MAX(C47,0)*Assumptions!$B$66</f>
-        <v>15.6417122611684</v>
-      </c>
-      <c r="D48" s="19" t="n">
-        <f aca="false">MAX(D47,0)*Assumptions!$B$66</f>
-        <v>16.0974161484536</v>
-      </c>
-      <c r="E48" s="19" t="n">
-        <f aca="false">MAX(E47,0)*Assumptions!$B$66</f>
-        <v>16.5595861438144</v>
-      </c>
-      <c r="F48" s="19" t="n">
-        <f aca="false">MAX(F47,0)*Assumptions!$B$66</f>
-        <v>17.0277295983402</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="B49" s="19" t="n">
-        <f aca="false">B43*Assumptions!$B$101</f>
-        <v>10.2666666666667</v>
-      </c>
-      <c r="C49" s="19" t="n">
-        <f aca="false">C43*Assumptions!$B$102</f>
-        <v>10.78</v>
-      </c>
-      <c r="D49" s="19" t="n">
-        <f aca="false">D43*Assumptions!$B$103</f>
-        <v>9.702</v>
-      </c>
-      <c r="E49" s="19" t="n">
-        <f aca="false">E43*Assumptions!$B$104</f>
-        <v>10.1871</v>
-      </c>
-      <c r="F49" s="19" t="n">
-        <f aca="false">F43*Assumptions!$B$105</f>
-        <v>10.696455</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="B50" s="19" t="n">
-        <f aca="false">(B43-Assumptions!$B$26)*Working_Capital!$B$16</f>
-        <v>5.05753424657534</v>
-      </c>
-      <c r="C50" s="19" t="n">
-        <f aca="false">(C43-B43)*Working_Capital!$B$16</f>
-        <v>2.13972602739726</v>
-      </c>
-      <c r="D50" s="19" t="n">
-        <f aca="false">(D43-C43)*Working_Capital!$B$16</f>
-        <v>2.24671232876713</v>
-      </c>
-      <c r="E50" s="19" t="n">
-        <f aca="false">(E43-D43)*Working_Capital!$B$16</f>
-        <v>2.35904794520548</v>
-      </c>
-      <c r="F50" s="19" t="n">
-        <f aca="false">(F43-E43)*Working_Capital!$B$16</f>
-        <v>2.47700034246575</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="B51" s="19" t="n">
+        <f aca="false">B48*Assumptions!$B$100</f>
+        <v>7.33333333333333</v>
+      </c>
+      <c r="C51" s="19" t="n">
+        <f aca="false">C48*Assumptions!$B$100</f>
+        <v>7.7</v>
+      </c>
+      <c r="D51" s="19" t="n">
+        <f aca="false">D48*Assumptions!$B$100</f>
+        <v>8.085</v>
+      </c>
+      <c r="E51" s="19" t="n">
+        <f aca="false">E48*Assumptions!$B$100</f>
+        <v>8.48925</v>
+      </c>
+      <c r="F51" s="19" t="n">
+        <f aca="false">F48*Assumptions!$B$100</f>
+        <v>8.9137125</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="B52" s="19" t="n">
+        <f aca="false">B50-B51</f>
+        <v>68.9333333333333</v>
+      </c>
+      <c r="C52" s="19" t="n">
+        <f aca="false">C50-C51</f>
+        <v>70.9696563573883</v>
+      </c>
+      <c r="D52" s="19" t="n">
+        <f aca="false">D50-D51</f>
+        <v>73.0372783505155</v>
+      </c>
+      <c r="E52" s="19" t="n">
+        <f aca="false">E50-E51</f>
+        <v>75.1342384020619</v>
+      </c>
+      <c r="F52" s="19" t="n">
+        <f aca="false">F50-F51</f>
+        <v>77.2583012628866</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="B53" s="19" t="n">
+        <f aca="false">MAX(B52,0)*Assumptions!$B$66</f>
+        <v>15.1929066666667</v>
+      </c>
+      <c r="C53" s="19" t="n">
+        <f aca="false">MAX(C52,0)*Assumptions!$B$66</f>
+        <v>15.6417122611684</v>
+      </c>
+      <c r="D53" s="19" t="n">
+        <f aca="false">MAX(D52,0)*Assumptions!$B$66</f>
+        <v>16.0974161484536</v>
+      </c>
+      <c r="E53" s="19" t="n">
+        <f aca="false">MAX(E52,0)*Assumptions!$B$66</f>
+        <v>16.5595861438144</v>
+      </c>
+      <c r="F53" s="19" t="n">
+        <f aca="false">MAX(F52,0)*Assumptions!$B$66</f>
+        <v>17.0277295983402</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B54" s="19" t="n">
+        <f aca="false">B48*Assumptions!$B$101</f>
+        <v>10.2666666666667</v>
+      </c>
+      <c r="C54" s="19" t="n">
+        <f aca="false">C48*Assumptions!$B$102</f>
+        <v>10.78</v>
+      </c>
+      <c r="D54" s="19" t="n">
+        <f aca="false">D48*Assumptions!$B$103</f>
+        <v>9.702</v>
+      </c>
+      <c r="E54" s="19" t="n">
+        <f aca="false">E48*Assumptions!$B$104</f>
+        <v>10.1871</v>
+      </c>
+      <c r="F54" s="19" t="n">
+        <f aca="false">F48*Assumptions!$B$105</f>
+        <v>10.696455</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="B55" s="19" t="n">
+        <f aca="false">(B48-Assumptions!$B$26)*Working_Capital!$B$16</f>
+        <v>5.05753424657534</v>
+      </c>
+      <c r="C55" s="19" t="n">
+        <f aca="false">(C48-B48)*Working_Capital!$B$16</f>
+        <v>2.13972602739726</v>
+      </c>
+      <c r="D55" s="19" t="n">
+        <f aca="false">(D48-C48)*Working_Capital!$B$16</f>
+        <v>2.24671232876713</v>
+      </c>
+      <c r="E55" s="19" t="n">
+        <f aca="false">(E48-D48)*Working_Capital!$B$16</f>
+        <v>2.35904794520548</v>
+      </c>
+      <c r="F55" s="19" t="n">
+        <f aca="false">(F48-E48)*Working_Capital!$B$16</f>
+        <v>2.47700034246575</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="B51" s="30" t="n">
+      <c r="B56" s="30" t="n">
         <f aca="false">Assumptions!$B$120</f>
         <v>8</v>
       </c>
-      <c r="C51" s="15" t="n">
+      <c r="C56" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D51" s="15" t="n">
+      <c r="D56" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="15" t="n">
+      <c r="E56" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F51" s="15" t="n">
+      <c r="F56" s="15" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="27" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="27" t="s">
         <v>313</v>
       </c>
-      <c r="B52" s="31" t="n">
-        <f aca="false">B45-B48-B49-B50-B51</f>
+      <c r="B57" s="31" t="n">
+        <f aca="false">B50-B53-B54-B55-B56</f>
         <v>37.749559086758</v>
       </c>
-      <c r="C52" s="31" t="n">
-        <f aca="false">C45-C48-C49-C50-C51</f>
+      <c r="C57" s="31" t="n">
+        <f aca="false">C50-C53-C54-C55-C56</f>
         <v>50.1082180688227</v>
       </c>
-      <c r="D52" s="31" t="n">
-        <f aca="false">D45-D48-D49-D50-D51</f>
+      <c r="D57" s="31" t="n">
+        <f aca="false">D50-D53-D54-D55-D56</f>
         <v>53.0761498732947</v>
       </c>
-      <c r="E52" s="31" t="n">
-        <f aca="false">E45-E48-E49-E50-E51</f>
+      <c r="E57" s="31" t="n">
+        <f aca="false">E50-E53-E54-E55-E56</f>
         <v>54.5177543130419</v>
       </c>
-      <c r="F52" s="31" t="n">
-        <f aca="false">F45-F48-F49-F50-F51</f>
+      <c r="F57" s="31" t="n">
+        <f aca="false">F50-F53-F54-F55-F56</f>
         <v>55.9708288220807</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="9" t="s">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="B53" s="34" t="n">
+      <c r="B58" s="34" t="n">
         <f aca="false">1/(1+Assumptions!$B$92)^1</f>
         <v>0.918932171410991</v>
       </c>
-      <c r="C53" s="34" t="n">
+      <c r="C58" s="34" t="n">
         <f aca="false">1/(1+Assumptions!$B$92)^2</f>
         <v>0.844436335654119</v>
       </c>
-      <c r="D53" s="34" t="n">
+      <c r="D58" s="34" t="n">
         <f aca="false">1/(1+Assumptions!$B$92)^3</f>
         <v>0.77597971554098</v>
       </c>
-      <c r="E53" s="34" t="n">
+      <c r="E58" s="34" t="n">
         <f aca="false">1/(1+Assumptions!$B$92)^4</f>
         <v>0.713072724972956</v>
       </c>
-      <c r="F53" s="34" t="n">
+      <c r="F58" s="34" t="n">
         <f aca="false">1/(1+Assumptions!$B$92)^5</f>
         <v>0.655265467533351</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="B54" s="19" t="n">
-        <f aca="false">B52*B53</f>
-        <v>34.689284301402</v>
-      </c>
-      <c r="C54" s="19" t="n">
-        <f aca="false">C52*C53</f>
-        <v>42.3132000521941</v>
-      </c>
-      <c r="D54" s="19" t="n">
-        <f aca="false">D52*D53</f>
-        <v>41.1860156806897</v>
-      </c>
-      <c r="E54" s="19" t="n">
-        <f aca="false">E52*E53</f>
-        <v>38.8751236274069</v>
-      </c>
-      <c r="F54" s="19" t="n">
-        <f aca="false">F52*F53</f>
-        <v>36.6757513163298</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="B56" s="19" t="n">
-        <f aca="false">SUM(B54:F54)</f>
-        <v>193.739374978023</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="B57" s="24" t="n">
-        <f aca="false">F44</f>
-        <v>0.241683848797251</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="B58" s="34" t="n">
-        <f aca="false">(B57-Assumptions!$B$100)*(1-Assumptions!$B$66)+Assumptions!$B$100-Assumptions!$B$106</f>
-        <v>0.163926728522337</v>
-      </c>
-    </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="9" t="s">
-        <v>318</v>
+        <v>260</v>
       </c>
       <c r="B59" s="19" t="n">
-        <f aca="false">F43*((1+Assumptions!$B$93)*B58-Assumptions!$B$93*Working_Capital!$B$16)/(Assumptions!$B$92-Assumptions!$B$93)</f>
-        <v>1007.23388384203</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="B60" s="19" t="n">
-        <f aca="false">B59*F53</f>
-        <v>660.005581811179</v>
+        <f aca="false">B57*B58</f>
+        <v>34.689284301402</v>
+      </c>
+      <c r="C59" s="19" t="n">
+        <f aca="false">C57*C58</f>
+        <v>42.3132000521941</v>
+      </c>
+      <c r="D59" s="19" t="n">
+        <f aca="false">D57*D58</f>
+        <v>41.1860156806897</v>
+      </c>
+      <c r="E59" s="19" t="n">
+        <f aca="false">E57*E58</f>
+        <v>38.8751236274069</v>
+      </c>
+      <c r="F59" s="19" t="n">
+        <f aca="false">F57*F58</f>
+        <v>36.6757513163298</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="27" t="s">
-        <v>273</v>
-      </c>
-      <c r="B61" s="36" t="n">
-        <f aca="false">B56+B60</f>
-        <v>853.744956789202</v>
+      <c r="A61" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="B61" s="19" t="n">
+        <f aca="false">SUM(B59:F59)</f>
+        <v>193.739374978023</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="B62" s="18" t="n">
-        <f aca="false">B60/B61</f>
-        <v>0.773071133905557</v>
+        <v>316</v>
+      </c>
+      <c r="B62" s="24" t="n">
+        <f aca="false">F49</f>
+        <v>0.241683848797251</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="B63" s="19" t="n">
-        <f aca="false">B52/(1+(Assumptions!$B$92+Assumptions!$B$94))^1+C52/(1+(Assumptions!$B$92+Assumptions!$B$94))^2+D52/(1+(Assumptions!$B$92+Assumptions!$B$94))^3+E52/(1+(Assumptions!$B$92+Assumptions!$B$94))^4+F52/(1+(Assumptions!$B$92+Assumptions!$B$94))^5+F43*((1+(Assumptions!$B$93-Assumptions!$B$95))*B58-(Assumptions!$B$93-Assumptions!$B$95)*Working_Capital!$B$16)/((Assumptions!$B$92+Assumptions!$B$94)-(Assumptions!$B$93-Assumptions!$B$95))/(1+(Assumptions!$B$92+Assumptions!$B$94))^5</f>
-        <v>741.287696792603</v>
+        <v>317</v>
+      </c>
+      <c r="B63" s="34" t="n">
+        <f aca="false">(B62-Assumptions!$B$100)*(1-Assumptions!$B$66)+Assumptions!$B$100-Assumptions!$B$106</f>
+        <v>0.163926728522337</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="9" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B64" s="19" t="n">
-        <f aca="false">B52/(1+(Assumptions!$B$92-Assumptions!$B$94))^1+C52/(1+(Assumptions!$B$92-Assumptions!$B$94))^2+D52/(1+(Assumptions!$B$92-Assumptions!$B$94))^3+E52/(1+(Assumptions!$B$92-Assumptions!$B$94))^4+F52/(1+(Assumptions!$B$92-Assumptions!$B$94))^5+F43*((1+(Assumptions!$B$93+Assumptions!$B$95))*B58-(Assumptions!$B$93+Assumptions!$B$95)*Working_Capital!$B$16)/((Assumptions!$B$92-Assumptions!$B$94)-(Assumptions!$B$93+Assumptions!$B$95))/(1+(Assumptions!$B$92-Assumptions!$B$94))^5</f>
-        <v>1012.33076501811</v>
+        <f aca="false">F48*((1+Assumptions!$B$93)*B63-Assumptions!$B$93*Working_Capital!$B$16)/(Assumptions!$B$92-Assumptions!$B$93)</f>
+        <v>1007.23388384203</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="9" t="s">
-        <v>322</v>
+        <v>271</v>
       </c>
       <c r="B65" s="19" t="n">
-        <f aca="false">(Assumptions!$B$10-B56)/F53</f>
-        <v>1535.65337238035</v>
+        <f aca="false">B64*F58</f>
+        <v>660.005581811179</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="B66" s="45" t="n">
-        <f aca="false">(((B65*(Assumptions!$B$92-Assumptions!$B$93)/F43+Assumptions!$B$93*Working_Capital!$B$16)/(1+Assumptions!$B$93))-Assumptions!$B$100+Assumptions!$B$106)/(1-Assumptions!$B$66)+Assumptions!$B$100</f>
-        <v>0.349137301487365</v>
-      </c>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
+      <c r="A66" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="B66" s="36" t="n">
+        <f aca="false">B61+B65</f>
+        <v>853.744956789202</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="B67" s="46" t="s">
-        <v>186</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="F67" s="6" t="s">
-        <v>190</v>
+      <c r="A67" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="B67" s="18" t="n">
+        <f aca="false">B65/B66</f>
+        <v>0.773071133905557</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="B68" s="19" t="n">
+        <f aca="false">B57/(1+(Assumptions!$B$92+Assumptions!$B$94))^1+C57/(1+(Assumptions!$B$92+Assumptions!$B$94))^2+D57/(1+(Assumptions!$B$92+Assumptions!$B$94))^3+E57/(1+(Assumptions!$B$92+Assumptions!$B$94))^4+F57/(1+(Assumptions!$B$92+Assumptions!$B$94))^5+F48*((1+(Assumptions!$B$93-Assumptions!$B$95))*B63-(Assumptions!$B$93-Assumptions!$B$95)*Working_Capital!$B$16)/((Assumptions!$B$92+Assumptions!$B$94)-(Assumptions!$B$93-Assumptions!$B$95))/(1+(Assumptions!$B$92+Assumptions!$B$94))^5</f>
+        <v>741.287696792603</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="B69" s="19" t="n">
+        <f aca="false">B57/(1+(Assumptions!$B$92-Assumptions!$B$94))^1+C57/(1+(Assumptions!$B$92-Assumptions!$B$94))^2+D57/(1+(Assumptions!$B$92-Assumptions!$B$94))^3+E57/(1+(Assumptions!$B$92-Assumptions!$B$94))^4+F57/(1+(Assumptions!$B$92-Assumptions!$B$94))^5+F48*((1+(Assumptions!$B$93+Assumptions!$B$95))*B63-(Assumptions!$B$93+Assumptions!$B$95)*Working_Capital!$B$16)/((Assumptions!$B$92-Assumptions!$B$94)-(Assumptions!$B$93+Assumptions!$B$95))/(1+(Assumptions!$B$92-Assumptions!$B$94))^5</f>
+        <v>1012.33076501811</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="B70" s="19" t="n">
+        <f aca="false">(Assumptions!$B$10-B61)/F58</f>
+        <v>1535.65337238035</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="B71" s="24" t="n">
+        <f aca="false">(((B70*(Assumptions!$B$92-Assumptions!$B$93)/F48+Assumptions!$B$93*Working_Capital!$B$16)/(1+Assumptions!$B$93))-Assumptions!$B$100+Assumptions!$B$106)/(1-Assumptions!$B$66)+Assumptions!$B$100</f>
+        <v>0.349137301487365</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="B72" s="24" t="n">
+        <f aca="false">(B70*Assumptions!$B$92-F48*B63)/(F48*(B63-Working_Capital!$B$16)+B70)</f>
+        <v>0.0499498648436709</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="B68" s="29" t="n">
+      <c r="B78" s="29" t="n">
         <f aca="false">Case_Drivers!$B$8</f>
         <v>0.03</v>
       </c>
-      <c r="C68" s="29" t="n">
+      <c r="C78" s="29" t="n">
         <f aca="false">Case_Drivers!$C$8</f>
         <v>0.03</v>
       </c>
-      <c r="D68" s="29" t="n">
+      <c r="D78" s="29" t="n">
         <f aca="false">Case_Drivers!$D$8</f>
         <v>0.03</v>
       </c>
-      <c r="E68" s="29" t="n">
+      <c r="E78" s="29" t="n">
         <f aca="false">Case_Drivers!$E$8</f>
         <v>0.03</v>
       </c>
-      <c r="F68" s="29" t="n">
+      <c r="F78" s="29" t="n">
         <f aca="false">Case_Drivers!$F$8</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="27" t="s">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="27" t="s">
         <v>226</v>
       </c>
-      <c r="B69" s="31" t="n">
-        <f aca="false">Assumptions!$B$26*(1+B68)</f>
+      <c r="B79" s="31" t="n">
+        <f aca="false">Assumptions!$B$26*(1+B78)</f>
         <v>266.426666666667</v>
       </c>
-      <c r="C69" s="31" t="n">
-        <f aca="false">B69*(1+C68)</f>
+      <c r="C79" s="31" t="n">
+        <f aca="false">B79*(1+C78)</f>
         <v>274.419466666667</v>
       </c>
-      <c r="D69" s="31" t="n">
-        <f aca="false">C69*(1+D68)</f>
+      <c r="D79" s="31" t="n">
+        <f aca="false">C79*(1+D78)</f>
         <v>282.652050666667</v>
       </c>
-      <c r="E69" s="31" t="n">
-        <f aca="false">D69*(1+E68)</f>
+      <c r="E79" s="31" t="n">
+        <f aca="false">D79*(1+E78)</f>
         <v>291.131612186667</v>
       </c>
-      <c r="F69" s="31" t="n">
-        <f aca="false">E69*(1+F68)</f>
+      <c r="F79" s="31" t="n">
+        <f aca="false">E79*(1+F78)</f>
         <v>299.865560552267</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="9" t="s">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="B70" s="29" t="n">
+      <c r="B80" s="29" t="n">
         <f aca="false">Case_Drivers!$B$14</f>
         <v>0.213367697594502</v>
       </c>
-      <c r="C70" s="29" t="n">
+      <c r="C80" s="29" t="n">
         <f aca="false">Case_Drivers!$C$14</f>
         <v>0.203367697594502</v>
       </c>
-      <c r="D70" s="29" t="n">
+      <c r="D80" s="29" t="n">
         <f aca="false">Case_Drivers!$D$14</f>
         <v>0.203367697594502</v>
       </c>
-      <c r="E70" s="29" t="n">
+      <c r="E80" s="29" t="n">
         <f aca="false">Case_Drivers!$E$14</f>
         <v>0.203367697594502</v>
       </c>
-      <c r="F70" s="29" t="n">
+      <c r="F80" s="29" t="n">
         <f aca="false">Case_Drivers!$F$14</f>
         <v>0.203367697594502</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="27" t="s">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="27" t="s">
         <v>244</v>
       </c>
-      <c r="B71" s="31" t="n">
-        <f aca="false">B69*B70</f>
+      <c r="B81" s="31" t="n">
+        <f aca="false">B79*B80</f>
         <v>56.8468444444445</v>
       </c>
-      <c r="C71" s="31" t="n">
-        <f aca="false">C69*C70</f>
+      <c r="C81" s="31" t="n">
+        <f aca="false">C79*C80</f>
         <v>55.8080551111111</v>
       </c>
-      <c r="D71" s="31" t="n">
-        <f aca="false">D69*D70</f>
+      <c r="D81" s="31" t="n">
+        <f aca="false">D79*D80</f>
         <v>57.4822967644445</v>
       </c>
-      <c r="E71" s="31" t="n">
-        <f aca="false">E69*E70</f>
+      <c r="E81" s="31" t="n">
+        <f aca="false">E79*E80</f>
         <v>59.2067656673778</v>
       </c>
-      <c r="F71" s="31" t="n">
-        <f aca="false">F69*F70</f>
+      <c r="F81" s="31" t="n">
+        <f aca="false">F79*F80</f>
         <v>60.9829686373991</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="9" t="s">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="B72" s="19" t="n">
-        <f aca="false">B69*Assumptions!$B$100</f>
+      <c r="B82" s="19" t="n">
+        <f aca="false">B79*Assumptions!$B$100</f>
         <v>6.66066666666667</v>
       </c>
-      <c r="C72" s="19" t="n">
-        <f aca="false">C69*Assumptions!$B$100</f>
+      <c r="C82" s="19" t="n">
+        <f aca="false">C79*Assumptions!$B$100</f>
         <v>6.86048666666667</v>
       </c>
-      <c r="D72" s="19" t="n">
-        <f aca="false">D69*Assumptions!$B$100</f>
+      <c r="D82" s="19" t="n">
+        <f aca="false">D79*Assumptions!$B$100</f>
         <v>7.06630126666667</v>
       </c>
-      <c r="E72" s="19" t="n">
-        <f aca="false">E69*Assumptions!$B$100</f>
+      <c r="E82" s="19" t="n">
+        <f aca="false">E79*Assumptions!$B$100</f>
         <v>7.27829030466667</v>
       </c>
-      <c r="F72" s="19" t="n">
-        <f aca="false">F69*Assumptions!$B$100</f>
+      <c r="F82" s="19" t="n">
+        <f aca="false">F79*Assumptions!$B$100</f>
         <v>7.49663901380667</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="9" t="s">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="B73" s="19" t="n">
-        <f aca="false">B71-B72</f>
+      <c r="B83" s="19" t="n">
+        <f aca="false">B81-B82</f>
         <v>50.1861777777778</v>
       </c>
-      <c r="C73" s="19" t="n">
-        <f aca="false">C71-C72</f>
+      <c r="C83" s="19" t="n">
+        <f aca="false">C81-C82</f>
         <v>48.9475684444445</v>
       </c>
-      <c r="D73" s="19" t="n">
-        <f aca="false">D71-D72</f>
+      <c r="D83" s="19" t="n">
+        <f aca="false">D81-D82</f>
         <v>50.4159954977778</v>
       </c>
-      <c r="E73" s="19" t="n">
-        <f aca="false">E71-E72</f>
+      <c r="E83" s="19" t="n">
+        <f aca="false">E81-E82</f>
         <v>51.9284753627111</v>
       </c>
-      <c r="F73" s="19" t="n">
-        <f aca="false">F71-F72</f>
+      <c r="F83" s="19" t="n">
+        <f aca="false">F81-F82</f>
         <v>53.4863296235925</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="9" t="s">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="B74" s="19" t="n">
-        <f aca="false">MAX(B73,0)*Assumptions!$B$66</f>
+      <c r="B84" s="19" t="n">
+        <f aca="false">MAX(B83,0)*Assumptions!$B$66</f>
         <v>11.0610335822222</v>
       </c>
-      <c r="C74" s="19" t="n">
-        <f aca="false">MAX(C73,0)*Assumptions!$B$66</f>
+      <c r="C84" s="19" t="n">
+        <f aca="false">MAX(C83,0)*Assumptions!$B$66</f>
         <v>10.7880440851556</v>
       </c>
-      <c r="D74" s="19" t="n">
-        <f aca="false">MAX(D73,0)*Assumptions!$B$66</f>
+      <c r="D84" s="19" t="n">
+        <f aca="false">MAX(D83,0)*Assumptions!$B$66</f>
         <v>11.1116854077102</v>
       </c>
-      <c r="E74" s="19" t="n">
-        <f aca="false">MAX(E73,0)*Assumptions!$B$66</f>
+      <c r="E84" s="19" t="n">
+        <f aca="false">MAX(E83,0)*Assumptions!$B$66</f>
         <v>11.4450359699415</v>
       </c>
-      <c r="F74" s="19" t="n">
-        <f aca="false">MAX(F73,0)*Assumptions!$B$66</f>
+      <c r="F84" s="19" t="n">
+        <f aca="false">MAX(F83,0)*Assumptions!$B$66</f>
         <v>11.7883870490398</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="9" t="s">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="B75" s="19" t="n">
-        <f aca="false">B69*Assumptions!$B$101</f>
+      <c r="B85" s="19" t="n">
+        <f aca="false">B79*Assumptions!$B$101</f>
         <v>9.32493333333333</v>
       </c>
-      <c r="C75" s="19" t="n">
-        <f aca="false">C69*Assumptions!$B$102</f>
+      <c r="C85" s="19" t="n">
+        <f aca="false">C79*Assumptions!$B$102</f>
         <v>9.60468133333333</v>
       </c>
-      <c r="D75" s="19" t="n">
-        <f aca="false">D69*Assumptions!$B$103</f>
+      <c r="D85" s="19" t="n">
+        <f aca="false">D79*Assumptions!$B$103</f>
         <v>8.47956152</v>
       </c>
-      <c r="E75" s="19" t="n">
-        <f aca="false">E69*Assumptions!$B$104</f>
+      <c r="E85" s="19" t="n">
+        <f aca="false">E79*Assumptions!$B$104</f>
         <v>8.7339483656</v>
       </c>
-      <c r="F75" s="19" t="n">
-        <f aca="false">F69*Assumptions!$B$105</f>
+      <c r="F85" s="19" t="n">
+        <f aca="false">F79*Assumptions!$B$105</f>
         <v>8.995966816568</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="9" t="s">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="B76" s="19" t="n">
-        <f aca="false">(B69-Assumptions!$B$26)*Working_Capital!$B$16</f>
+      <c r="B86" s="19" t="n">
+        <f aca="false">(B79-Assumptions!$B$26)*Working_Capital!$B$16</f>
         <v>1.13210958904109</v>
       </c>
-      <c r="C76" s="19" t="n">
-        <f aca="false">(C69-B69)*Working_Capital!$B$16</f>
+      <c r="C86" s="19" t="n">
+        <f aca="false">(C79-B79)*Working_Capital!$B$16</f>
         <v>1.16607287671233</v>
       </c>
-      <c r="D76" s="19" t="n">
-        <f aca="false">(D69-C69)*Working_Capital!$B$16</f>
+      <c r="D86" s="19" t="n">
+        <f aca="false">(D79-C79)*Working_Capital!$B$16</f>
         <v>1.2010550630137</v>
       </c>
-      <c r="E76" s="19" t="n">
-        <f aca="false">(E69-D69)*Working_Capital!$B$16</f>
+      <c r="E86" s="19" t="n">
+        <f aca="false">(E79-D79)*Working_Capital!$B$16</f>
         <v>1.23708671490411</v>
       </c>
-      <c r="F76" s="19" t="n">
-        <f aca="false">(F69-E69)*Working_Capital!$B$16</f>
+      <c r="F86" s="19" t="n">
+        <f aca="false">(F79-E79)*Working_Capital!$B$16</f>
         <v>1.27419931635123</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="9" t="s">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="B77" s="30" t="n">
+      <c r="B87" s="30" t="n">
         <f aca="false">Assumptions!$B$120</f>
         <v>8</v>
       </c>
-      <c r="C77" s="15" t="n">
+      <c r="C87" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D77" s="15" t="n">
+      <c r="D87" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E77" s="15" t="n">
+      <c r="E87" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F77" s="15" t="n">
+      <c r="F87" s="15" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="27" t="s">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="27" t="s">
         <v>313</v>
       </c>
-      <c r="B78" s="31" t="n">
-        <f aca="false">B71-B74-B75-B76-B77</f>
+      <c r="B88" s="31" t="n">
+        <f aca="false">B81-B84-B85-B86-B87</f>
         <v>27.3287679398478</v>
       </c>
-      <c r="C78" s="31" t="n">
-        <f aca="false">C71-C74-C75-C76-C77</f>
+      <c r="C88" s="31" t="n">
+        <f aca="false">C81-C84-C85-C86-C87</f>
         <v>34.2492568159099</v>
       </c>
-      <c r="D78" s="31" t="n">
-        <f aca="false">D71-D74-D75-D76-D77</f>
+      <c r="D88" s="31" t="n">
+        <f aca="false">D81-D84-D85-D86-D87</f>
         <v>36.6899947737205</v>
       </c>
-      <c r="E78" s="31" t="n">
-        <f aca="false">E71-E74-E75-E76-E77</f>
+      <c r="E88" s="31" t="n">
+        <f aca="false">E81-E84-E85-E86-E87</f>
         <v>37.7906946169322</v>
       </c>
-      <c r="F78" s="31" t="n">
-        <f aca="false">F71-F74-F75-F76-F77</f>
+      <c r="F88" s="31" t="n">
+        <f aca="false">F81-F84-F85-F86-F87</f>
         <v>38.9244154554401</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="9" t="s">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="B79" s="34" t="n">
+      <c r="B89" s="34" t="n">
         <f aca="false">1/(1+Assumptions!$B$92)^1</f>
         <v>0.918932171410991</v>
       </c>
-      <c r="C79" s="34" t="n">
+      <c r="C89" s="34" t="n">
         <f aca="false">1/(1+Assumptions!$B$92)^2</f>
         <v>0.844436335654119</v>
       </c>
-      <c r="D79" s="34" t="n">
+      <c r="D89" s="34" t="n">
         <f aca="false">1/(1+Assumptions!$B$92)^3</f>
         <v>0.77597971554098</v>
       </c>
-      <c r="E79" s="34" t="n">
+      <c r="E89" s="34" t="n">
         <f aca="false">1/(1+Assumptions!$B$92)^4</f>
         <v>0.713072724972956</v>
       </c>
-      <c r="F79" s="34" t="n">
+      <c r="F89" s="34" t="n">
         <f aca="false">1/(1+Assumptions!$B$92)^5</f>
         <v>0.655265467533351</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="B80" s="19" t="n">
-        <f aca="false">B78*B79</f>
-        <v>25.1132840649514</v>
-      </c>
-      <c r="C80" s="19" t="n">
-        <f aca="false">C78*C79</f>
-        <v>28.9213169245038</v>
-      </c>
-      <c r="D80" s="19" t="n">
-        <f aca="false">D78*D79</f>
-        <v>28.4706917077117</v>
-      </c>
-      <c r="E80" s="19" t="n">
-        <f aca="false">E78*E79</f>
-        <v>26.9475135891166</v>
-      </c>
-      <c r="F80" s="19" t="n">
-        <f aca="false">F78*F79</f>
-        <v>25.5058252918713</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="B82" s="19" t="n">
-        <f aca="false">SUM(B80:F80)</f>
-        <v>134.958631578155</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="B83" s="24" t="n">
-        <f aca="false">F70</f>
-        <v>0.203367697594502</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="B84" s="34" t="n">
-        <f aca="false">(B83-Assumptions!$B$100)*(1-Assumptions!$B$66)+Assumptions!$B$100-Assumptions!$B$106</f>
-        <v>0.134055457044674</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="B85" s="19" t="n">
-        <f aca="false">F69*((1+Assumptions!$B$93)*B84-Assumptions!$B$93*Working_Capital!$B$16)/(Assumptions!$B$92-Assumptions!$B$93)</f>
-        <v>688.636608961644</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="B86" s="19" t="n">
-        <f aca="false">B85*F79</f>
-        <v>451.239789531833</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="27" t="s">
-        <v>273</v>
-      </c>
-      <c r="B87" s="36" t="n">
-        <f aca="false">B82+B86</f>
-        <v>586.198421109987</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="B88" s="18" t="n">
-        <f aca="false">B86/B87</f>
-        <v>0.769773123369036</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="B89" s="19" t="n">
-        <f aca="false">B78/(1+(Assumptions!$B$92+Assumptions!$B$94))^1+C78/(1+(Assumptions!$B$92+Assumptions!$B$94))^2+D78/(1+(Assumptions!$B$92+Assumptions!$B$94))^3+E78/(1+(Assumptions!$B$92+Assumptions!$B$94))^4+F78/(1+(Assumptions!$B$92+Assumptions!$B$94))^5+F69*((1+(Assumptions!$B$93-Assumptions!$B$95))*B84-(Assumptions!$B$93-Assumptions!$B$95)*Working_Capital!$B$16)/((Assumptions!$B$92+Assumptions!$B$94)-(Assumptions!$B$93-Assumptions!$B$95))/(1+(Assumptions!$B$92+Assumptions!$B$94))^5</f>
-        <v>509.658320109114</v>
-      </c>
-    </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="9" t="s">
-        <v>321</v>
+        <v>260</v>
       </c>
       <c r="B90" s="19" t="n">
-        <f aca="false">B78/(1+(Assumptions!$B$92-Assumptions!$B$94))^1+C78/(1+(Assumptions!$B$92-Assumptions!$B$94))^2+D78/(1+(Assumptions!$B$92-Assumptions!$B$94))^3+E78/(1+(Assumptions!$B$92-Assumptions!$B$94))^4+F78/(1+(Assumptions!$B$92-Assumptions!$B$94))^5+F69*((1+(Assumptions!$B$93+Assumptions!$B$95))*B84-(Assumptions!$B$93+Assumptions!$B$95)*Working_Capital!$B$16)/((Assumptions!$B$92-Assumptions!$B$94)-(Assumptions!$B$93+Assumptions!$B$95))/(1+(Assumptions!$B$92-Assumptions!$B$94))^5</f>
-        <v>694.097258352378</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="B91" s="19" t="n">
-        <f aca="false">(Assumptions!$B$10-B82)/F79</f>
-        <v>1625.35860836835</v>
+        <f aca="false">B88*B89</f>
+        <v>25.1132840649514</v>
+      </c>
+      <c r="C90" s="19" t="n">
+        <f aca="false">C88*C89</f>
+        <v>28.9213169245038</v>
+      </c>
+      <c r="D90" s="19" t="n">
+        <f aca="false">D88*D89</f>
+        <v>28.4706917077117</v>
+      </c>
+      <c r="E90" s="19" t="n">
+        <f aca="false">E88*E89</f>
+        <v>26.9475135891166</v>
+      </c>
+      <c r="F90" s="19" t="n">
+        <f aca="false">F88*F89</f>
+        <v>25.5058252918713</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="B92" s="24" t="n">
-        <f aca="false">(((B91*(Assumptions!$B$92-Assumptions!$B$93)/F69+Assumptions!$B$93*Working_Capital!$B$16)/(1+Assumptions!$B$93))-Assumptions!$B$100+Assumptions!$B$106)/(1-Assumptions!$B$66)+Assumptions!$B$100</f>
-        <v>0.429855225778457</v>
+        <v>315</v>
+      </c>
+      <c r="B92" s="19" t="n">
+        <f aca="false">SUM(B90:F90)</f>
+        <v>134.958631578155</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="9" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="B93" s="24" t="n">
-        <f aca="false">(B91*Assumptions!$B$92-F69*B84)/(F69*(B84-Working_Capital!$B$16)+B91)</f>
+        <f aca="false">F80</f>
+        <v>0.203367697594502</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="B94" s="34" t="n">
+        <f aca="false">(B93-Assumptions!$B$100)*(1-Assumptions!$B$66)+Assumptions!$B$100-Assumptions!$B$106</f>
+        <v>0.134055457044674</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="B95" s="19" t="n">
+        <f aca="false">F79*((1+Assumptions!$B$93)*B94-Assumptions!$B$93*Working_Capital!$B$16)/(Assumptions!$B$92-Assumptions!$B$93)</f>
+        <v>688.636608961644</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="B96" s="19" t="n">
+        <f aca="false">B95*F89</f>
+        <v>451.239789531833</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="B97" s="36" t="n">
+        <f aca="false">B92+B96</f>
+        <v>586.198421109987</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="B98" s="18" t="n">
+        <f aca="false">B96/B97</f>
+        <v>0.769773123369036</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="B99" s="19" t="n">
+        <f aca="false">B88/(1+(Assumptions!$B$92+Assumptions!$B$94))^1+C88/(1+(Assumptions!$B$92+Assumptions!$B$94))^2+D88/(1+(Assumptions!$B$92+Assumptions!$B$94))^3+E88/(1+(Assumptions!$B$92+Assumptions!$B$94))^4+F88/(1+(Assumptions!$B$92+Assumptions!$B$94))^5+F79*((1+(Assumptions!$B$93-Assumptions!$B$95))*B94-(Assumptions!$B$93-Assumptions!$B$95)*Working_Capital!$B$16)/((Assumptions!$B$92+Assumptions!$B$94)-(Assumptions!$B$93-Assumptions!$B$95))/(1+(Assumptions!$B$92+Assumptions!$B$94))^5</f>
+        <v>509.658320109114</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="B100" s="19" t="n">
+        <f aca="false">B88/(1+(Assumptions!$B$92-Assumptions!$B$94))^1+C88/(1+(Assumptions!$B$92-Assumptions!$B$94))^2+D88/(1+(Assumptions!$B$92-Assumptions!$B$94))^3+E88/(1+(Assumptions!$B$92-Assumptions!$B$94))^4+F88/(1+(Assumptions!$B$92-Assumptions!$B$94))^5+F79*((1+(Assumptions!$B$93+Assumptions!$B$95))*B94-(Assumptions!$B$93+Assumptions!$B$95)*Working_Capital!$B$16)/((Assumptions!$B$92-Assumptions!$B$94)-(Assumptions!$B$93+Assumptions!$B$95))/(1+(Assumptions!$B$92-Assumptions!$B$94))^5</f>
+        <v>694.097258352378</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="B101" s="19" t="n">
+        <f aca="false">(Assumptions!$B$10-B92)/F89</f>
+        <v>1625.35860836835</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="B102" s="24" t="n">
+        <f aca="false">(((B101*(Assumptions!$B$92-Assumptions!$B$93)/F79+Assumptions!$B$93*Working_Capital!$B$16)/(1+Assumptions!$B$93))-Assumptions!$B$100+Assumptions!$B$106)/(1-Assumptions!$B$66)+Assumptions!$B$100</f>
+        <v>0.429855225778457</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="B103" s="24" t="n">
+        <f aca="false">(B101*Assumptions!$B$92-F79*B94)/(F79*(B94-Working_Capital!$B$16)+B101)</f>
         <v>0.0636263740870107</v>
       </c>
     </row>
